--- a/YRIGOYEN 9730/Octubre/YRIGOYEN7630-Octubre.xlsx
+++ b/YRIGOYEN 9730/Octubre/YRIGOYEN7630-Octubre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9730\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9730\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FA899B-4E6E-4302-BCCF-B3A1672B5091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EC6701-4550-4046-9A80-1ABA31030E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="120">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -320,9 +320,6 @@
     <t>Honorarios administracion</t>
   </si>
   <si>
-    <t>Transf 26/08</t>
-  </si>
-  <si>
     <t>Subidos en Agost000</t>
   </si>
   <si>
@@ -332,49 +329,64 @@
     <t>Federacion patronal  Seguro obligatorio de consorcio</t>
   </si>
   <si>
-    <t>PENDIENTE PASAR COSAS DE DOARTERO ARREGLO DPTO AGUSTIN</t>
-  </si>
-  <si>
-    <t>VTO 15/10</t>
-  </si>
-  <si>
-    <t>PERÍODO: SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>Ascensores lema - Mantenimiento agosto</t>
   </si>
   <si>
     <t>Transf 11/09</t>
   </si>
   <si>
-    <t>Gustavo padron - Sr contador honorarios SEPTIEMBRE</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fumigacion </t>
   </si>
   <si>
-    <t>Debito 08/09</t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Debito 12/09</t>
-  </si>
-  <si>
-    <t>Debito 16/09</t>
-  </si>
-  <si>
-    <t>Debito 04/09</t>
-  </si>
-  <si>
-    <t>Doartero Julio  - Cambio de cañeria interna del baño completa y ramal cloacal (Dpto. 10)</t>
-  </si>
-  <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Transf 14/10</t>
+  </si>
+  <si>
+    <t>VTO 14/11</t>
+  </si>
+  <si>
+    <t>PERÍODO: OCTUBRE</t>
+  </si>
+  <si>
+    <t>Gustavo padron - Sr contador honorarios OCTUBRE</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de OCTUBRE</t>
+  </si>
+  <si>
+    <t>Debito 02/10</t>
+  </si>
+  <si>
+    <t>Debito 08/10</t>
+  </si>
+  <si>
+    <t>Debito 13/10</t>
+  </si>
+  <si>
+    <t>Debito 16/10</t>
+  </si>
+  <si>
+    <t>Federacion patronal - Seguro de vida obligatorio Sr. Walter</t>
+  </si>
+  <si>
+    <t>Debito 17/10</t>
+  </si>
+  <si>
+    <t>Debito 20/10</t>
+  </si>
+  <si>
+    <t>Punitorios de periodos pago fuera de terminos</t>
+  </si>
+  <si>
+    <t>Debito 29/10</t>
+  </si>
+  <si>
+    <t>Transf 29/10</t>
   </si>
 </sst>
 </file>
@@ -1343,7 +1355,6 @@
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1353,6 +1364,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1428,9 +1442,7 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1854,7 +1866,7 @@
         <v>60</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="73" t="s">
@@ -1875,7 +1887,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" s="195" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C8" s="195"/>
     </row>
@@ -1948,7 +1960,7 @@
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="160">
-        <v>748673</v>
+        <v>760763</v>
       </c>
       <c r="E22" s="5"/>
     </row>
@@ -1967,7 +1979,7 @@
       <c r="C24" s="59"/>
       <c r="D24" s="169">
         <f>SUM(D22:D23)</f>
-        <v>748673</v>
+        <v>760763</v>
       </c>
       <c r="E24" s="144"/>
       <c r="G24" s="22"/>
@@ -2059,7 +2071,7 @@
       <c r="D34" s="172"/>
       <c r="E34" s="145">
         <f>D24+D33</f>
-        <v>748673</v>
+        <v>760763</v>
       </c>
       <c r="F34" s="22"/>
     </row>
@@ -2074,13 +2086,12 @@
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="190" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B36" s="191"/>
       <c r="C36" s="54"/>
       <c r="D36" s="160">
-        <f>30000</f>
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="E36" s="147"/>
     </row>
@@ -2095,7 +2106,7 @@
       </c>
       <c r="E37" s="147"/>
       <c r="H37" s="158" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2107,7 +2118,7 @@
       <c r="D38" s="175"/>
       <c r="E38" s="148">
         <f>SUM(D36:D37)</f>
-        <v>142400</v>
+        <v>147400</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -2121,7 +2132,7 @@
     </row>
     <row r="40" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="188" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B40" s="189"/>
       <c r="C40" s="56"/>
@@ -2129,287 +2140,285 @@
         <v>26570</v>
       </c>
       <c r="E40" s="161" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="188" t="s">
-        <v>100</v>
-      </c>
-      <c r="B41" s="189"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="166" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" s="159"/>
       <c r="C41" s="56"/>
-      <c r="D41" s="178">
+      <c r="D41" s="177">
+        <v>6152</v>
+      </c>
+      <c r="E41" s="161" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="188" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" s="189"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="178">
         <v>54278</v>
       </c>
-      <c r="E41" s="150" t="str">
+      <c r="E42" s="150" t="str">
         <f>E40</f>
-        <v>Debito 04/09</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="30" t="s">
+        <v>Debito 02/10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="175"/>
-      <c r="E42" s="151">
-        <f>SUM(D40:D41)</f>
-        <v>80848</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="36" t="s">
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="175"/>
+      <c r="E43" s="151">
+        <f>SUM(D40:D42)</f>
+        <v>87000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="152"/>
-      <c r="C43" s="152"/>
-      <c r="D43" s="179"/>
-      <c r="E43" s="153"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="54"/>
-      <c r="D44" s="180">
-        <v>562727.52</v>
-      </c>
-      <c r="E44" s="161" t="s">
-        <v>109</v>
-      </c>
-      <c r="G44" s="127"/>
+      <c r="B44" s="152"/>
+      <c r="C44" s="152"/>
+      <c r="D44" s="179"/>
+      <c r="E44" s="153"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="54"/>
-      <c r="D45" s="180">
-        <v>10602.27</v>
+      <c r="D45" s="211">
+        <v>544619.34</v>
       </c>
       <c r="E45" s="161" t="s">
-        <v>112</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="G45" s="127"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="54"/>
-      <c r="D46" s="180">
-        <v>75532.289999999994</v>
-      </c>
-      <c r="E46" s="161" t="str">
-        <f>E45</f>
-        <v>Debito 16/09</v>
-      </c>
-      <c r="G46" s="143"/>
+      <c r="D46" s="211">
+        <v>119008</v>
+      </c>
+      <c r="E46" s="161" t="s">
+        <v>118</v>
+      </c>
+      <c r="G46" s="127"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="164">
-        <v>79308.399999999994</v>
+      <c r="C47" s="54"/>
+      <c r="D47" s="211">
+        <v>10602.27</v>
       </c>
       <c r="E47" s="161" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="str">
-        <f>A47</f>
-        <v>Sindicatos mes de SEPTIEMBRE</v>
+      <c r="A48" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="164">
-        <v>5140.8</v>
-      </c>
-      <c r="E48" s="162" t="str">
+      <c r="C48" s="54"/>
+      <c r="D48" s="211">
+        <v>75532.289999999994</v>
+      </c>
+      <c r="E48" s="161" t="str">
         <f>E47</f>
-        <v>Debito 12/09</v>
-      </c>
+        <v>Debito 16/10</v>
+      </c>
+      <c r="G48" s="143"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="str">
-        <f>A48</f>
-        <v>Sindicatos mes de SEPTIEMBRE</v>
+      <c r="A49" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="164">
-        <v>46261.66</v>
-      </c>
-      <c r="E49" s="163" t="str">
-        <f>E48</f>
-        <v>Debito 12/09</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="30" t="s">
+        <v>77379.429999999993</v>
+      </c>
+      <c r="E49" s="161" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="str">
+        <f>A49</f>
+        <v>Sindicatos mes de OCTUBRE</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="164">
+        <v>4974.57</v>
+      </c>
+      <c r="E50" s="162" t="str">
+        <f>E49</f>
+        <v>Debito 13/10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="str">
+        <f>A50</f>
+        <v>Sindicatos mes de OCTUBRE</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="164">
+        <v>44771.13</v>
+      </c>
+      <c r="E51" s="163" t="str">
+        <f>E50</f>
+        <v>Debito 13/10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B50" s="152"/>
-      <c r="C50" s="152"/>
-      <c r="D50" s="181"/>
-      <c r="E50" s="151">
-        <f>SUM(D44:D49)</f>
-        <v>779572.94000000018</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="36" t="s">
+      <c r="B52" s="152"/>
+      <c r="C52" s="152"/>
+      <c r="D52" s="180"/>
+      <c r="E52" s="151">
+        <f>SUM(D45:D51)</f>
+        <v>876887.03</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B51" s="152"/>
-      <c r="C51" s="152"/>
-      <c r="D51" s="179"/>
-      <c r="E51" s="153"/>
-    </row>
-    <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
+      <c r="B53" s="152"/>
+      <c r="C53" s="152"/>
+      <c r="D53" s="179"/>
+      <c r="E53" s="153"/>
+    </row>
+    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="164">
-        <v>48142.59</v>
-      </c>
-      <c r="E52" s="161" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B53" s="164"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="164">
-        <v>0</v>
-      </c>
-      <c r="E53" s="211" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="164">
-        <v>26472.2</v>
+        <v>54234.99</v>
       </c>
       <c r="E54" s="161" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="188" t="s">
-        <v>80</v>
-      </c>
-      <c r="B55" s="189"/>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B55" s="164"/>
       <c r="C55" s="5"/>
       <c r="D55" s="164">
-        <v>303116.46999999997</v>
-      </c>
-      <c r="E55" s="165" t="s">
-        <v>106</v>
+        <v>27593.64</v>
+      </c>
+      <c r="E55" s="185" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="188" t="s">
-        <v>80</v>
-      </c>
-      <c r="B56" s="189"/>
+      <c r="A56" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="164">
-        <v>309335.53999999998</v>
-      </c>
-      <c r="E56" s="165" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="30" t="s">
+        <v>26441.68</v>
+      </c>
+      <c r="E56" s="161" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="188" t="s">
+        <v>80</v>
+      </c>
+      <c r="B57" s="189"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="164">
+        <v>426357.06</v>
+      </c>
+      <c r="E57" s="165" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="182"/>
-      <c r="E57" s="151">
-        <f>SUM(D52:D56)</f>
-        <v>687066.79999999993</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="36"/>
       <c r="B58" s="30"/>
       <c r="C58" s="30"/>
-      <c r="D58" s="175"/>
-      <c r="E58" s="154"/>
-    </row>
-    <row r="59" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="166" t="s">
-        <v>105</v>
-      </c>
-      <c r="B59" s="159"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="164">
-        <v>71200</v>
-      </c>
-      <c r="E59" s="165" t="s">
-        <v>106</v>
-      </c>
+      <c r="D58" s="181"/>
+      <c r="E58" s="151">
+        <f>SUM(D54:D57)</f>
+        <v>534627.37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="36"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="175"/>
+      <c r="E59" s="154"/>
     </row>
     <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="166" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B60" s="159"/>
       <c r="C60" s="5"/>
       <c r="D60" s="164">
-        <v>65500</v>
+        <v>77500</v>
       </c>
       <c r="E60" s="165" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="190" t="s">
-        <v>114</v>
-      </c>
-      <c r="B61" s="191"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="166" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" s="159"/>
       <c r="C61" s="5"/>
       <c r="D61" s="164">
-        <v>1050000</v>
+        <v>61350</v>
       </c>
       <c r="E61" s="165" t="s">
-        <v>97</v>
-      </c>
-      <c r="H61" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="188" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B62" s="189"/>
       <c r="C62" s="5"/>
       <c r="D62" s="109">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="E62" s="165" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I62" s="188"/>
       <c r="J62" s="189"/>
@@ -2422,8 +2431,8 @@
       <c r="C63" s="36"/>
       <c r="D63" s="35"/>
       <c r="E63" s="155">
-        <f>SUM(D59:D62)</f>
-        <v>1226700</v>
+        <f>SUM(D60:D62)</f>
+        <v>138850</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2453,7 +2462,7 @@
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
       <c r="D66" s="164">
-        <v>56008.43</v>
+        <v>62873.69</v>
       </c>
       <c r="E66" s="41"/>
     </row>
@@ -2466,7 +2475,7 @@
       <c r="D67" s="112"/>
       <c r="E67" s="106">
         <f>SUM(D65:D66)</f>
-        <v>109008.43</v>
+        <v>115873.69</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2483,7 +2492,10 @@
       <c r="B69" s="31"/>
       <c r="C69" s="31"/>
       <c r="D69" s="114"/>
-      <c r="E69" s="115"/>
+      <c r="E69" s="115">
+        <f>3774269.17-2661401.09</f>
+        <v>1112868.08</v>
+      </c>
     </row>
     <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
@@ -2500,7 +2512,7 @@
       <c r="D71" s="118"/>
       <c r="E71" s="119">
         <f>(SUM(E27:E69))</f>
-        <v>3774269.1700000004</v>
+        <v>3774269.17</v>
       </c>
       <c r="F71" s="143"/>
       <c r="G71" s="45"/>
@@ -2512,7 +2524,7 @@
     <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D73" s="116"/>
       <c r="E73" s="116"/>
-      <c r="H73" s="183"/>
+      <c r="H73" s="182"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
@@ -2592,7 +2604,7 @@
       </c>
       <c r="B86" s="103">
         <f>E71</f>
-        <v>3774269.1700000004</v>
+        <v>3774269.17</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2601,7 +2613,7 @@
       </c>
       <c r="B87" s="103">
         <f>E71-E69</f>
-        <v>3774269.1700000004</v>
+        <v>2661401.09</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2665,7 +2677,7 @@
       </c>
       <c r="B98" s="41">
         <f>PRORRATEO!F29</f>
-        <v>2888514.2500000005</v>
+        <v>3982800.4400000004</v>
       </c>
       <c r="C98" s="24"/>
     </row>
@@ -2704,7 +2716,7 @@
       </c>
       <c r="B103" s="49">
         <f>-B87</f>
-        <v>-3774269.1700000004</v>
+        <v>-2661401.09</v>
       </c>
       <c r="C103" s="24"/>
     </row>
@@ -2724,7 +2736,7 @@
       </c>
       <c r="B105" s="61">
         <f>SUM(B97:B104)</f>
-        <v>-885754.91999999993</v>
+        <v>1321399.3500000006</v>
       </c>
       <c r="C105" s="27"/>
       <c r="D105" s="45"/>
@@ -2750,7 +2762,7 @@
         <v>91</v>
       </c>
       <c r="B109" s="135">
-        <v>-215085.03609999688</v>
+        <v>-1100839.9560999968</v>
       </c>
       <c r="C109" s="38"/>
       <c r="D109" s="48"/>
@@ -2761,7 +2773,7 @@
       </c>
       <c r="B110" s="140">
         <f>-B87</f>
-        <v>-3774269.1700000004</v>
+        <v>-2661401.09</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -2788,14 +2800,14 @@
       </c>
       <c r="B113" s="141">
         <f>PRORRATEO!F29</f>
-        <v>2888514.2500000005</v>
+        <v>3982800.4400000004</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="B114" s="184"/>
+      <c r="B114" s="183"/>
     </row>
     <row r="115" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="138" t="s">
@@ -2803,7 +2815,7 @@
       </c>
       <c r="B115" s="139">
         <f>SUM(B109:C114)</f>
-        <v>-1100839.9560999968</v>
+        <v>220559.39390000375</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
@@ -2879,19 +2891,17 @@
       <c r="E127" s="186"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A56:B56"/>
+  <mergeCells count="16">
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="I62:J62"/>
-    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A57:B57"/>
     <mergeCell ref="A124:E127"/>
     <mergeCell ref="A118:C119"/>
     <mergeCell ref="A92:E94"/>
@@ -3045,7 +3055,7 @@
       <c r="K5" s="210"/>
       <c r="L5" s="63" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 15/10</v>
+        <v>VTO 14/11</v>
       </c>
       <c r="M5" s="205"/>
       <c r="N5" s="197"/>
@@ -3062,11 +3072,11 @@
         <v>6.69</v>
       </c>
       <c r="E6" s="76">
-        <v>239912.01</v>
+        <v>258261.01</v>
       </c>
       <c r="F6" s="78">
         <f>E6</f>
-        <v>239912.01</v>
+        <v>258261.01</v>
       </c>
       <c r="G6" s="79">
         <f t="shared" ref="G6:G23" si="0">E6-F6</f>
@@ -3116,19 +3126,16 @@
         <v>5.88</v>
       </c>
       <c r="E7" s="76">
-        <v>330100.02</v>
-      </c>
-      <c r="F7" s="78">
-        <f>100000</f>
-        <v>100000</v>
-      </c>
+        <v>463995.02</v>
+      </c>
+      <c r="F7" s="78"/>
       <c r="G7" s="79">
         <f t="shared" si="0"/>
-        <v>230100.02000000002</v>
+        <v>463995.02</v>
       </c>
       <c r="H7" s="79">
         <f t="shared" ref="H7:H23" si="2">IF(G7&gt;0,G7*3%,0)</f>
-        <v>6903.0006000000003</v>
+        <v>13919.8506</v>
       </c>
       <c r="I7" s="80">
         <v>0</v>
@@ -3143,15 +3150,15 @@
       </c>
       <c r="L7" s="83">
         <f t="shared" ref="L7:L23" si="4">ROUND(SUM(G7:K7),0) + O7</f>
-        <v>463995.02</v>
+        <v>704907.02</v>
       </c>
       <c r="M7" s="84">
         <f t="shared" ref="M7:M23" si="5">ROUND(L7*6% + L7,0) + O7</f>
-        <v>491835.02</v>
+        <v>747201.02</v>
       </c>
       <c r="N7" s="85">
         <f t="shared" ref="N7:N23" si="6">ROUND(L7*3%,0) + L7</f>
-        <v>477915.02</v>
+        <v>726054.02</v>
       </c>
       <c r="O7" s="45">
         <f>O6+0.01</f>
@@ -3172,19 +3179,18 @@
         <v>6.65</v>
       </c>
       <c r="E8" s="76">
-        <v>238478.03</v>
+        <v>264419.03000000003</v>
       </c>
       <c r="F8" s="78">
-        <f>E8</f>
-        <v>238478.03</v>
+        <v>256717</v>
       </c>
       <c r="G8" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7702.0300000000279</v>
       </c>
       <c r="H8" s="79">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>231.06090000000083</v>
       </c>
       <c r="I8" s="80">
         <v>0</v>
@@ -3199,15 +3205,15 @@
       </c>
       <c r="L8" s="83">
         <f t="shared" si="4"/>
-        <v>256717.03</v>
+        <v>264650.03000000003</v>
       </c>
       <c r="M8" s="84">
         <f t="shared" si="5"/>
-        <v>272120.03000000003</v>
+        <v>280529.03000000003</v>
       </c>
       <c r="N8" s="85">
         <f t="shared" si="6"/>
-        <v>264419.03000000003</v>
+        <v>272590.03000000003</v>
       </c>
       <c r="O8" s="45">
         <f t="shared" ref="O8:O24" si="8">O7+0.01</f>
@@ -3227,11 +3233,11 @@
         <v>6.73</v>
       </c>
       <c r="E9" s="76">
-        <v>241347.04</v>
+        <v>259805.04</v>
       </c>
       <c r="F9" s="78">
         <f t="shared" ref="F9:F23" si="9">E9</f>
-        <v>241347.04</v>
+        <v>259805.04</v>
       </c>
       <c r="G9" s="79">
         <f t="shared" si="0"/>
@@ -3283,16 +3289,19 @@
         <v>8.0399999999999991</v>
       </c>
       <c r="E10" s="76">
-        <v>288325.05</v>
-      </c>
-      <c r="F10" s="78"/>
+        <v>607351.05000000005</v>
+      </c>
+      <c r="F10" s="78">
+        <f>288325.05+320000</f>
+        <v>608325.05000000005</v>
+      </c>
       <c r="G10" s="79">
         <f t="shared" si="0"/>
-        <v>288325.05</v>
+        <v>-974</v>
       </c>
       <c r="H10" s="79">
         <f t="shared" si="2"/>
-        <v>8649.7514999999985</v>
+        <v>0</v>
       </c>
       <c r="I10" s="80">
         <v>0</v>
@@ -3307,15 +3316,15 @@
       </c>
       <c r="L10" s="83">
         <f t="shared" si="4"/>
-        <v>607351.05000000005</v>
+        <v>309402.05</v>
       </c>
       <c r="M10" s="84">
         <f t="shared" si="5"/>
-        <v>643792.05000000005</v>
+        <v>327966.05</v>
       </c>
       <c r="N10" s="85">
         <f t="shared" si="6"/>
-        <v>625572.05000000005</v>
+        <v>318684.05</v>
       </c>
       <c r="O10" s="45">
         <f t="shared" si="8"/>
@@ -3336,11 +3345,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="E11" s="76">
-        <v>169624.06</v>
+        <v>182597.06</v>
       </c>
       <c r="F11" s="78">
         <f t="shared" si="9"/>
-        <v>169624.06</v>
+        <v>182597.06</v>
       </c>
       <c r="G11" s="79">
         <f t="shared" si="0"/>
@@ -3391,11 +3400,11 @@
         <v>5.67</v>
       </c>
       <c r="E12" s="76">
-        <v>203334.07</v>
+        <v>218885.07</v>
       </c>
       <c r="F12" s="78">
         <f>E12</f>
-        <v>203334.07</v>
+        <v>218885.07</v>
       </c>
       <c r="G12" s="79">
         <f t="shared" si="0"/>
@@ -3446,19 +3455,19 @@
         <v>5.67</v>
       </c>
       <c r="E13" s="76">
-        <v>204008.08</v>
+        <v>321893.08</v>
       </c>
       <c r="F13" s="78">
-        <f>104000</f>
-        <v>104000</v>
+        <f>160000</f>
+        <v>160000</v>
       </c>
       <c r="G13" s="79">
         <f t="shared" si="0"/>
-        <v>100008.07999999999</v>
+        <v>161893.08000000002</v>
       </c>
       <c r="H13" s="79">
         <f t="shared" si="2"/>
-        <v>3000.2423999999996</v>
+        <v>4856.7924000000003</v>
       </c>
       <c r="I13" s="80">
         <v>0</v>
@@ -3473,15 +3482,15 @@
       </c>
       <c r="L13" s="83">
         <f t="shared" si="4"/>
-        <v>321893.08</v>
+        <v>385635.08</v>
       </c>
       <c r="M13" s="84">
         <f t="shared" si="5"/>
-        <v>341207.08</v>
+        <v>408773.08</v>
       </c>
       <c r="N13" s="85">
         <f t="shared" si="6"/>
-        <v>331550.08000000002</v>
+        <v>397204.08</v>
       </c>
       <c r="O13" s="45">
         <f t="shared" si="8"/>
@@ -3504,11 +3513,11 @@
         <v>7.67</v>
       </c>
       <c r="E14" s="76">
-        <v>275057.09000000003</v>
+        <v>296093.09000000003</v>
       </c>
       <c r="F14" s="78">
         <f t="shared" si="9"/>
-        <v>275057.09000000003</v>
+        <v>296093.09000000003</v>
       </c>
       <c r="G14" s="79">
         <f t="shared" si="0"/>
@@ -3559,11 +3568,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="E15" s="76">
-        <v>185695.1</v>
+        <v>189160.1</v>
       </c>
       <c r="F15" s="78">
         <f>E15</f>
-        <v>185695.1</v>
+        <v>189160.1</v>
       </c>
       <c r="G15" s="79">
         <f t="shared" si="0"/>
@@ -3614,11 +3623,11 @@
         <v>5.63</v>
       </c>
       <c r="E16" s="76">
-        <v>201899.11</v>
+        <v>217341.11</v>
       </c>
       <c r="F16" s="78">
         <f t="shared" si="9"/>
-        <v>201899.11</v>
+        <v>217341.11</v>
       </c>
       <c r="G16" s="79">
         <f t="shared" si="0"/>
@@ -3669,11 +3678,11 @@
         <v>5.55</v>
       </c>
       <c r="E17" s="76">
-        <v>199030.12</v>
+        <v>214252.12</v>
       </c>
       <c r="F17" s="78">
         <f t="shared" si="9"/>
-        <v>199030.12</v>
+        <v>214252.12</v>
       </c>
       <c r="G17" s="79">
         <f t="shared" si="0"/>
@@ -3724,11 +3733,11 @@
         <v>11.06</v>
       </c>
       <c r="E18" s="76">
-        <v>396626.13</v>
+        <v>426961.13</v>
       </c>
       <c r="F18" s="78">
         <f>E18</f>
-        <v>396626.13</v>
+        <v>426961.13</v>
       </c>
       <c r="G18" s="79">
         <f t="shared" si="0"/>
@@ -3779,16 +3788,18 @@
         <v>3.3</v>
       </c>
       <c r="E19" s="76">
-        <v>216771.14</v>
-      </c>
-      <c r="F19" s="78"/>
+        <v>350668.14</v>
+      </c>
+      <c r="F19" s="78">
+        <v>50000</v>
+      </c>
       <c r="G19" s="79">
         <f t="shared" si="0"/>
-        <v>216771.14</v>
+        <v>300668.14</v>
       </c>
       <c r="H19" s="79">
         <f t="shared" si="2"/>
-        <v>6503.1342000000004</v>
+        <v>9020.0442000000003</v>
       </c>
       <c r="I19" s="80">
         <v>0</v>
@@ -3803,15 +3814,15 @@
       </c>
       <c r="L19" s="83">
         <f t="shared" si="4"/>
-        <v>350668.14</v>
+        <v>437082.14</v>
       </c>
       <c r="M19" s="84">
         <f t="shared" si="5"/>
-        <v>371708.14</v>
+        <v>463307.14</v>
       </c>
       <c r="N19" s="85">
         <f t="shared" si="6"/>
-        <v>361188.14</v>
+        <v>450194.14</v>
       </c>
       <c r="O19" s="45">
         <f t="shared" si="8"/>
@@ -3831,11 +3842,11 @@
         <v>1.8</v>
       </c>
       <c r="E20" s="76">
-        <v>64550.15</v>
+        <v>69487.149999999994</v>
       </c>
       <c r="F20" s="78">
         <f>E20</f>
-        <v>64550.15</v>
+        <v>69487.149999999994</v>
       </c>
       <c r="G20" s="79">
         <f t="shared" si="0"/>
@@ -3886,11 +3897,11 @@
         <v>3.22</v>
       </c>
       <c r="E21" s="76">
-        <v>115474.16</v>
+        <v>124305.16</v>
       </c>
       <c r="F21" s="78">
         <f>E21</f>
-        <v>115474.16</v>
+        <v>124305.16</v>
       </c>
       <c r="G21" s="79">
         <f t="shared" si="0"/>
@@ -3942,16 +3953,19 @@
         <v>2.61</v>
       </c>
       <c r="E22" s="77">
-        <v>179251.17</v>
-      </c>
-      <c r="F22" s="78"/>
+        <v>285385.17</v>
+      </c>
+      <c r="F22" s="78">
+        <f>E22</f>
+        <v>285385.17</v>
+      </c>
       <c r="G22" s="79">
         <f t="shared" si="0"/>
-        <v>179251.17</v>
+        <v>0</v>
       </c>
       <c r="H22" s="79">
         <f t="shared" si="2"/>
-        <v>5377.5351000000001</v>
+        <v>0</v>
       </c>
       <c r="I22" s="80">
         <v>0</v>
@@ -3966,15 +3980,15 @@
       </c>
       <c r="L22" s="83">
         <f t="shared" si="4"/>
-        <v>285385.17</v>
+        <v>100757.17</v>
       </c>
       <c r="M22" s="84">
         <f t="shared" si="5"/>
-        <v>302508.17</v>
+        <v>106803.17</v>
       </c>
       <c r="N22" s="85">
         <f t="shared" si="6"/>
-        <v>293947.17</v>
+        <v>103780.17</v>
       </c>
       <c r="O22" s="45">
         <f t="shared" si="8"/>
@@ -3994,11 +4008,11 @@
         <v>4.28</v>
       </c>
       <c r="E23" s="76">
-        <v>153487.18</v>
+        <v>165225.18</v>
       </c>
       <c r="F23" s="78">
         <f t="shared" si="9"/>
-        <v>153487.18</v>
+        <v>165225.18</v>
       </c>
       <c r="G23" s="79">
         <f t="shared" si="0"/>
@@ -4134,19 +4148,19 @@
       </c>
       <c r="E29" s="55">
         <f>SUM(E6:E28)</f>
-        <v>3902969.7100000004</v>
+        <v>4916084.71</v>
       </c>
       <c r="F29" s="64">
         <f>SUM(F6:F28)</f>
-        <v>2888514.2500000005</v>
+        <v>3982800.4400000004</v>
       </c>
       <c r="G29" s="64">
         <f>SUM(G6:G28)</f>
-        <v>1014455.4600000001</v>
+        <v>933284.27000000014</v>
       </c>
       <c r="H29" s="64">
         <f t="shared" ref="H29:M29" si="10">SUM(H6:H28)</f>
-        <v>30433.663799999998</v>
+        <v>28027.748100000001</v>
       </c>
       <c r="I29" s="64">
         <f t="shared" si="10"/>
@@ -4162,15 +4176,15 @@
       </c>
       <c r="L29" s="100">
         <f>SUM(L6:L23)</f>
-        <v>4908382.71</v>
+        <v>4824806.71</v>
       </c>
       <c r="M29" s="100">
         <f t="shared" si="10"/>
-        <v>5202887.71</v>
+        <v>5114296.71</v>
       </c>
       <c r="N29" s="100">
         <f>SUM(N6:N28)</f>
-        <v>5055637.71</v>
+        <v>4969552.71</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4288,7 +4302,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="5" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C5" s="185" t="s">
+      <c r="C5" s="184" t="s">
         <v>92</v>
       </c>
       <c r="E5" t="s">
